--- a/files/九龙-何文田-瑜一第IC期.xlsx
+++ b/files/九龙-何文田-瑜一第IC期.xlsx
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>48280000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>39967</v>
+        <v>40000</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>48280000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>39967</v>
+        <v>40000</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -14183,9 +14183,9 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>B | 1208呎 (4+房)
+          <t>B | 1207呎 (4+房)
 $4828万
-$39,967/呎
+$40,000/呎
 (26年-07月-03日)</t>
         </is>
       </c>
